--- a/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Delphine est dans la cuisine. Maman range le buffet. Un petit pot fermé est sur la table. Delphine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman. Delphine dit : maman, je peux. Avant de goûter l'inconnu, il faut demander. Delphine va demander à l'adulte. Maman prend le pot. Maman dit : c'est du miel. Tu peux goûter. Delphine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Delphine pose les mains sur ses genoux. Maman range le pot. Delphine sourit. On demande à un adulte.</t>
+          <t>Delphine est dans la cuisine. Maman range le buffet. Un petit pot fermé est sur la table. Delphine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman. Maman, je peux. Avant de goûter l'inconnu, il faut demander. Delphine va demander à l'adulte. Maman prend le pot. C'est du miel. Tu peux goûter. Delphine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Delphine pose les mains sur ses genoux. Maman range le pot. Delphine sourit. On demande à un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Delphine est dans la cuisine. Maman range le buffet. Un petit pot fermé est sur la table. Delphine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman.
+enfant-f|Maman, je peux. Avant de goûter l'inconnu, il faut demander.
+narrateur|Delphine va demander à l'adulte. Maman prend le pot.
+maman|C'est du miel. Tu peux goûter.
+narrateur|Delphine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Delphine pose les mains sur ses genoux. Maman range le pot. Delphine sourit. On demande à un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1473,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Delphine voit un pot inconnu. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1645,6 +1675,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Delphine a demandé. L'adulte a répondu. Le pot inconnu, on en parle à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Delphine boit une gorgée d'eau. Maman range le pot.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Delphine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Delphine pose les mains sur ses genoux. Maman range le pot. Delphine sourit. On demande à un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1515,7 @@
           <t>narrateur|Delphine voit un pot inconnu. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1680,6 +1691,7 @@
           <t>narrateur|Delphine a demandé. L'adulte a répondu. Le pot inconnu, on en parle à maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1859,7 @@
           <t>narrateur|Delphine boit une gorgée d'eau. Maman range le pot.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2027,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2070,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2285,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Delphine demande avant de goûter</t>
+          <t>Le yaourt de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rayon barre le carrelage. Mila voit un petit pot fermé. Elle demande à maman. C'est du yaourt. Elle goûte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Delphine est dans la cuisine. Maman range le buffet. Un petit pot fermé est sur la table. Delphine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman. Maman, je peux. Avant de goûter l'inconnu, il faut demander. Delphine va demander à l'adulte. Maman prend le pot. C'est du miel. Tu peux goûter. Delphine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Delphine pose les mains sur ses genoux. Maman range le pot. Delphine sourit. On demande à un adulte.</t>
+          <t>Un rayon jaune barre le carrelage. Le buffet fait un petit cri en s'ouvrant. Une cuillère repose sur un linge blanc. Ça sent le lait froid. Mila, tu as vu le rayon ? Oui, maman. Il est jaune. Il est jaune, et tout chaud. La cuisine est calme, cet après-midi. Un tabouret bas attend près de la table. Tu veux ton tabouret ? Oui, maman. Mila pousse le tabouret. Le bois fait un petit bruit. Bravo. Tu es bien. Maman range le buffet. Les pots s'alignent tout doux. En ce moment, Mila est près de la table. Un petit pot fermé est sur la table. Le couvercle est lisse. Mila ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Mila va demander à l'adulte. Maman prend le pot. C'est du yaourt. Tu peux goûter. Mila goûte une petite cuillère. C'est frais et doux. C'est frais, maman. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Mila. Mila pose les mains sur ses genoux. Tu as fini de goûter ? Oui, maman. Bravo. Tu as fait du bon travail. Maman range le pot. Le rayon jaune est encore sur le carrelage. La cuillère brille sur le linge. Le tabouret est encore près de la table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Delphine est dans la cuisine. Maman range le buffet. Un petit pot fermé est sur la table. Delphine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman.
-enfant-f|Maman, je peux. Avant de goûter l'inconnu, il faut demander.
-narrateur|Delphine va demander à l'adulte. Maman prend le pot.
-maman|C'est du miel. Tu peux goûter.
-narrateur|Delphine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Delphine pose les mains sur ses genoux. Maman range le pot. Delphine sourit. On demande à un adulte.</t>
+          <t>narrateur|Un rayon jaune barre le carrelage.
+narrateur|Le buffet fait un petit cri en s'ouvrant.
+narrateur|Une cuillère repose sur un linge blanc.
+narrateur|Ça sent le lait froid.
+maman|Mila, tu as vu le rayon ?
+enfant-f|Oui, maman. Il est jaune.
+maman|Il est jaune, et tout chaud.
+narrateur|La cuisine est calme, cet après-midi.
+narrateur|Un tabouret bas attend près de la table.
+maman|Tu veux ton tabouret ?
+enfant-f|Oui, maman.
+narrateur|Mila pousse le tabouret.
+narrateur|Le bois fait un petit bruit.
+maman|Bravo. Tu es bien.
+narrateur|Maman range le buffet.
+narrateur|Les pots s'alignent tout doux.
+narrateur|En ce moment, Mila est près de la table.
+narrateur|Un petit pot fermé est sur la table.
+narrateur|Le couvercle est lisse.
+narrateur|Mila ne le connaît pas.
+narrateur|C'est de l'inconnu.
+narrateur|Elle a envie de goûter.
+narrateur|Elle pose les mains sur ses genoux.
+narrateur|Elle va vers maman.
+enfant-f|Maman, je peux ?
+maman|Tu demandes. C'est bien.
+narrateur|Avant de goûter l'inconnu, il faut demander.
+narrateur|Mila va demander à l'adulte.
+narrateur|Maman prend le pot.
+maman|C'est du yaourt.
+maman|Tu peux goûter.
+narrateur|Mila goûte une petite cuillère.
+narrateur|C'est frais et doux.
+enfant-f|C'est frais, maman.
+maman|Oui. Parce que tu as demandé.
+maman|On demande à un adulte.
+maman|Bravo, Mila.
+narrateur|Mila pose les mains sur ses genoux.
+maman|Tu as fini de goûter ?
+enfant-f|Oui, maman.
+maman|Bravo. Tu as fait du bon travail.
+narrateur|Maman range le pot.
+narrateur|Le rayon jaune est encore sur le carrelage.
+narrateur|La cuillère brille sur le linge.
+narrateur|Le tabouret est encore près de la table.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Delphine voit un pot inconnu. Que fait-elle ?</t>
+          <t>Mila voit un pot inconnu. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1512,10 +1564,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Delphine voit un pot inconnu. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila voit un pot inconnu.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1540,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Delphine a demandé. L'adulte a répondu. Le pot inconnu, on en parle à maman.</t>
+          <t>Mila a demandé. L'adulte a répondu. Le pot inconnu, on en parle à maman. Tu as demandé à maman ? Oui. Bravo. On demande à un adulte. Ça sent encore le lait froid. Le rayon jaune n'a pas bougé. Le tabouret est calme. Tes mains étaient sur tes genoux ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1688,10 +1740,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Delphine a demandé. L'adulte a répondu. Le pot inconnu, on en parle à maman.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a demandé.
+narrateur|L'adulte a répondu.
+narrateur|Le pot inconnu, on en parle à maman.
+maman|Tu as demandé à maman ?
+enfant-f|Oui.
+maman|Bravo.
+maman|On demande à un adulte.
+narrateur|Ça sent encore le lait froid.
+narrateur|Le rayon jaune n'a pas bougé.
+narrateur|Le tabouret est calme.
+maman|Tes mains étaient sur tes genoux ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1716,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Delphine boit une gorgée d'eau. Maman range le pot.</t>
+          <t>Mila boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Bravo. Tu as fait du bon travail. Maman range le pot. Le buffet est refermé. Le linge blanc est encore sur la table.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1856,10 +1918,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Delphine boit une gorgée d'eau. Maman range le pot.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Mila boit une gorgée d'eau.
+narrateur|L'eau est fraîche.
+maman|Le pot est rangé ?
+enfant-f|Oui, maman.
+maman|Bravo. Tu as fait du bon travail.
+narrateur|Maman range le pot.
+narrateur|Le buffet est refermé.
+narrateur|Le linge blanc est encore sur la table.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1884,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a vu un pot inconnu. Elle a demandé à maman. C'était du yaourt. Bravo, Mila. C'était frais. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2024,10 +2092,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Mila a vu un pot inconnu.
+narrateur|Elle a demandé à maman.
+narrateur|C'était du yaourt.
+maman|Bravo, Mila.
+enfant-f|C'était frais.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2046,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2084,6 +2156,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon jaune barre le carrelage. Le buffet fait un petit cri en s'ouvrant. Une cuillère repose sur un linge blanc. Ça sent le lait froid. Mila, tu as vu le rayon ? Oui, maman. Il est jaune. Il est jaune, et tout chaud. La cuisine est calme, cet après-midi. Un tabouret bas attend près de la table. Tu veux ton tabouret ? Oui, maman. Mila pousse le tabouret. Le bois fait un petit bruit. Bravo. Tu es bien. Maman range le buffet. Les pots s'alignent tout doux. En ce moment, Mila est près de la table. Un petit pot fermé est sur la table. Le couvercle est lisse. Mila ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Mila va demander à l'adulte. Maman prend le pot. C'est du yaourt. Tu peux goûter. Mila goûte une petite cuillère. C'est frais et doux. C'est frais, maman. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Mila. Mila pose les mains sur ses genoux. Tu as fini de goûter ? Oui, maman. Bravo. Tu as fait du bon travail. Maman range le pot. Le rayon jaune est encore sur le carrelage. La cuillère brille sur le linge. Le tabouret est encore près de la table.</t>
+          <t>Un rayon jaune barre le carrelage. Le buffet fait un petit cri en s'ouvrant. Une cuillère repose sur un linge blanc. Ça sent le lait froid. Mila, tu as vu le rayon ? Oui, maman. Il est jaune. Il est jaune, et tout chaud. La cuisine est calme, cet après-midi. Un tabouret bas attend près de la table. Tu veux ton tabouret ? Oui, maman. Mila pousse le tabouret. Le bois fait un petit bruit. Bravo. Tu es bien. Maman range le buffet. Les pots s'alignent tout doux. En ce moment, Mila est près de la table. Un petit pot fermé est sur la table. Le couvercle est lisse. Mila ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Mila va demander à l'adulte. Maman prend le pot. C'est du yaourt. Tu peux goûter. Mila goûte une petite cuillère. C'est frais et doux. C'est frais, maman. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Mila. Mila pose les mains sur ses genoux. Tu as fini de goûter ? Oui, maman. Maman range le pot. Le rayon jaune est encore sur le carrelage. La cuillère brille sur le linge. Le tabouret est encore près de la table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Delphine est dans la cuisine. Maman range le buffet. Un petit pot fermé est sur la table. Delphine ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle va vers maman. Delphine dit : maman, je peux. Avant de goûter l'inconnu, il faut &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Delphine va demander à l'adulte. Maman prend le pot. Maman dit : c'est du miel. Tu peux goûter. Delphine goûte une petite cuillère. C'est sucré. Parce qu'elle a demandé, maman a dit oui. Delphine pose les mains sur ses genoux. Maman range le pot. Delphine sourit. On demande à un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon jaune barre le carrelage. Le buffet fait un petit cri en s'ouvrant. Une cuillère repose sur un linge blanc. Ça sent le lait froid. Mila, tu as vu le rayon ? Oui, maman. Il est jaune. Il est jaune, et tout chaud. La cuisine est calme, cet après-midi. Un tabouret bas attend près de la table. Tu veux ton tabouret ? Oui, maman. Mila pousse le tabouret. Le bois fait un petit bruit. Bravo. Tu es bien. Maman range le buffet. Les pots s'alignent tout doux. En ce moment, Mila est près de la table. Un petit pot fermé est sur la table. Le couvercle est lisse. Mila ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Mila va demander à l'adulte. Maman prend le pot. C'est du yaourt. Tu peux goûter. Mila goûte une petite cuillère. C'est frais et doux. C'est frais, maman. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Mila. Mila pose les mains sur ses genoux. Tu as fini de goûter ? Oui, maman. Maman range le pot. Le rayon jaune est encore sur le carrelage. La cuillère brille sur le linge. Le tabouret est encore près de la table.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 narrateur|Mila pose les mains sur ses genoux.
 maman|Tu as fini de goûter ?
 enfant-f|Oui, maman.
-maman|Bravo. Tu as fait du bon travail.
 narrateur|Maman range le pot.
 narrateur|Le rayon jaune est encore sur le carrelage.
 narrateur|La cuillère brille sur le linge.
@@ -1405,7 +1404,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Delphine voit un pot &lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila voit un pot inconnu. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1597,7 +1596,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Delphine a demandé. L'adulte a répondu. Le pot &lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;, on en parle à maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a demandé. L'adulte a répondu. Le pot inconnu, on en parle à maman. Tu as demandé à maman ? Oui. Bravo. On demande à un adulte. Ça sent encore le lait froid. Le rayon jaune n'a pas bougé. Le tabouret est calme. Tes mains étaient sur tes genoux ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1778,12 +1777,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mila boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Bravo. Tu as fait du bon travail. Maman range le pot. Le buffet est refermé. Le linge blanc est encore sur la table.</t>
+          <t>Mila boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Maman range le pot. Le buffet est refermé. Le linge blanc est encore sur la table.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Delphine boit une gorgée d'eau. Maman range le pot.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Maman range le pot. Le buffet est refermé. Le linge blanc est encore sur la table.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1922,7 +1921,6 @@
 narrateur|L'eau est fraîche.
 maman|Le pot est rangé ?
 enfant-f|Oui, maman.
-maman|Bravo. Tu as fait du bon travail.
 narrateur|Maman range le pot.
 narrateur|Le buffet est refermé.
 narrateur|Le linge blanc est encore sur la table.</t>
@@ -1952,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mila a vu un pot inconnu. Elle a demandé à maman. C'était du yaourt. Bravo, Mila. C'était frais. L'histoire est finie.</t>
+          <t>Mila a vu un pot inconnu. Elle a demandé à maman. C'était du yaourt. Bravo, Mila. C'était frais.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a vu un pot inconnu. Elle a demandé à maman. C'était du yaourt. Bravo, Mila. C'était frais.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2096,8 +2094,7 @@
 narrateur|Elle a demandé à maman.
 narrateur|C'était du yaourt.
 maman|Bravo, Mila.
-enfant-f|C'était frais.
-narrateur|L'histoire est finie.</t>
+enfant-f|C'était frais.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Delphine, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le yaourt de Mila</t>
+          <t>Le miel de la crêpe</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine d'immeuble, lumière de la cour, crêpe dans la poêle</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Un rayon barre le carrelage. Mila voit un petit pot fermé. Elle demande à maman. C'est du yaourt. Elle goûte.</t>
+          <t>Mila veut une crêpe avec quelque chose de doux. Un petit pot doré n'a pas d'étiquette. Elle tend la main. La main de maman attend. Mila dit je peux. Elles goûtent le miel.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon jaune barre le carrelage. Le buffet fait un petit cri en s'ouvrant. Une cuillère repose sur un linge blanc. Ça sent le lait froid. Mila, tu as vu le rayon ? Oui, maman. Il est jaune. Il est jaune, et tout chaud. La cuisine est calme, cet après-midi. Un tabouret bas attend près de la table. Tu veux ton tabouret ? Oui, maman. Mila pousse le tabouret. Le bois fait un petit bruit. Bravo. Tu es bien. Maman range le buffet. Les pots s'alignent tout doux. En ce moment, Mila est près de la table. Un petit pot fermé est sur la table. Le couvercle est lisse. Mila ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Mila va demander à l'adulte. Maman prend le pot. C'est du yaourt. Tu peux goûter. Mila goûte une petite cuillère. C'est frais et doux. C'est frais, maman. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Mila. Mila pose les mains sur ses genoux. Tu as fini de goûter ? Oui, maman. Maman range le pot. Le rayon jaune est encore sur le carrelage. La cuillère brille sur le linge. Le tabouret est encore près de la table.</t>
+          <t>Une crêpe dore dans la poêle. Le beurre chante tout bas. La lumière de la cour entre, pâle. Un seau d'eau brille cinq étages plus bas. Ça sent la farine chaude. Tu as vu la crêpe, Mila ? Elle fait des trous, maman. C'est le beurre. Je veux la manger. Avec quelque chose de doux. On va lui trouver un ami ? Oui. En ce moment, Mila pousse le tabouret. Le bois racle le carrelage, tout doux. Un petit pot doré est sur la table. Il n'a pas d'étiquette. Le verre est lisse, un peu collant. Qu'est-ce que c'est ? Mila tend le doigt vers le couvercle. La main de maman s'arrête à côté. Elle n'attrape pas. Elle attend, ouverte, tout près. Le doigt de Mila s'arrête aussi. Maman, je peux ? Oui. On ouvre ensemble. Le couvercle colle un peu. Puis il vient. Une odeur de fleurs monte, épaisse. Ça sent l'été. C'est du miel. Tu goûtes avec moi ? Oui. Deux cuillères trempent, toutes lentes. Le fil d'or tombe, tout long. C'est collant. Et doux. Merci, Mila. Tu as attendu ma main. Maman pose la crêpe dans l'assiette. Le miel glisse au milieu, tout lent. Pour moi ? Pour toi. Mila plie la crêpe. Le miel coule un peu sur le pouce. C'est bon. La cour est calme, en bas ? Le seau brille encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon jaune barre le carrelage. Le buffet fait un petit cri en s'ouvrant. Une cuillère repose sur un linge blanc. Ça sent le lait froid. Mila, tu as vu le rayon ? Oui, maman. Il est jaune. Il est jaune, et tout chaud. La cuisine est calme, cet après-midi. Un tabouret bas attend près de la table. Tu veux ton tabouret ? Oui, maman. Mila pousse le tabouret. Le bois fait un petit bruit. Bravo. Tu es bien. Maman range le buffet. Les pots s'alignent tout doux. En ce moment, Mila est près de la table. Un petit pot fermé est sur la table. Le couvercle est lisse. Mila ne le connaît pas. C'est de l'inconnu. Elle a envie de goûter. Elle pose les mains sur ses genoux. Elle va vers maman. Maman, je peux ? Tu demandes. C'est bien. Avant de goûter l'inconnu, il faut demander. Mila va demander à l'adulte. Maman prend le pot. C'est du yaourt. Tu peux goûter. Mila goûte une petite cuillère. C'est frais et doux. C'est frais, maman. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Mila. Mila pose les mains sur ses genoux. Tu as fini de goûter ? Oui, maman. Maman range le pot. Le rayon jaune est encore sur le carrelage. La cuillère brille sur le linge. Le tabouret est encore près de la table.</t>
+          <t>Une crêpe dore dans la poêle. Le beurre chante tout bas. La lumière de la cour entre, pâle. Un seau d'eau brille cinq étages plus bas. Ça sent la farine chaude. Tu as vu la crêpe, Mila ? Elle fait des trous, maman. C'est le beurre. Je veux la manger. Avec quelque chose de doux. On va lui trouver un ami ? Oui. En ce moment, Mila pousse le tabouret. Le bois racle le carrelage, tout doux. Un petit pot doré est sur la table. Il n'a pas d'étiquette. Le verre est lisse, un peu collant. Qu'est-ce que c'est ? Mila tend le doigt vers le couvercle. La main de maman s'arrête à côté. Elle n'attrape pas. Elle attend, ouverte, tout près. Le doigt de Mila s'arrête aussi. Maman, je peux ? Oui. On ouvre ensemble. Le couvercle colle un peu. Puis il vient. Une odeur de fleurs monte, épaisse. Ça sent l'été. C'est du miel. Tu goûtes avec moi ? Oui. Deux cuillères trempent, toutes lentes. Le fil d'or tombe, tout long. C'est collant. Et doux. Merci, Mila. Tu as attendu ma main. Maman pose la crêpe dans l'assiette. Le miel glisse au milieu, tout lent. Pour moi ? Pour toi. Mila plie la crêpe. Le miel coule un peu sur le pouce. C'est bon. La cour est calme, en bas ? Le seau brille encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,50 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Un rayon jaune barre le carrelage.
-narrateur|Le buffet fait un petit cri en s'ouvrant.
-narrateur|Une cuillère repose sur un linge blanc.
-narrateur|Ça sent le lait froid.
-maman|Mila, tu as vu le rayon ?
-enfant-f|Oui, maman. Il est jaune.
-maman|Il est jaune, et tout chaud.
-narrateur|La cuisine est calme, cet après-midi.
-narrateur|Un tabouret bas attend près de la table.
-maman|Tu veux ton tabouret ?
-enfant-f|Oui, maman.
-narrateur|Mila pousse le tabouret.
-narrateur|Le bois fait un petit bruit.
-maman|Bravo. Tu es bien.
-narrateur|Maman range le buffet.
-narrateur|Les pots s'alignent tout doux.
-narrateur|En ce moment, Mila est près de la table.
-narrateur|Un petit pot fermé est sur la table.
-narrateur|Le couvercle est lisse.
-narrateur|Mila ne le connaît pas.
-narrateur|C'est de l'inconnu.
-narrateur|Elle a envie de goûter.
-narrateur|Elle pose les mains sur ses genoux.
-narrateur|Elle va vers maman.
+          <t>narrateur|Une crêpe dore dans la poêle.
+narrateur|Le beurre chante tout bas.
+narrateur|La lumière de la cour entre, pâle.
+narrateur|Un seau d'eau brille cinq étages plus bas.
+narrateur|Ça sent la farine chaude.
+maman|Tu as vu la crêpe, Mila ?
+enfant-f|Elle fait des trous, maman.
+maman|C'est le beurre.
+enfant-f|Je veux la manger.
+enfant-f|Avec quelque chose de doux.
+maman|On va lui trouver un ami ?
+enfant-f|Oui.
+narrateur|En ce moment, Mila pousse le tabouret.
+narrateur|Le bois racle le carrelage, tout doux.
+narrateur|Un petit pot doré est sur la table.
+narrateur|Il n'a pas d'étiquette.
+narrateur|Le verre est lisse, un peu collant.
+enfant-f|Qu'est-ce que c'est ?
+narrateur|Mila tend le doigt vers le couvercle.
+narrateur|La main de maman s'arrête à côté.
+narrateur|Elle n'attrape pas.
+narrateur|Elle attend, ouverte, tout près.
+narrateur|Le doigt de Mila s'arrête aussi.
 enfant-f|Maman, je peux ?
-maman|Tu demandes. C'est bien.
-narrateur|Avant de goûter l'inconnu, il faut demander.
-narrateur|Mila va demander à l'adulte.
-narrateur|Maman prend le pot.
-maman|C'est du yaourt.
-maman|Tu peux goûter.
-narrateur|Mila goûte une petite cuillère.
-narrateur|C'est frais et doux.
-enfant-f|C'est frais, maman.
-maman|Oui. Parce que tu as demandé.
-maman|On demande à un adulte.
-maman|Bravo, Mila.
-narrateur|Mila pose les mains sur ses genoux.
-maman|Tu as fini de goûter ?
-enfant-f|Oui, maman.
-narrateur|Maman range le pot.
-narrateur|Le rayon jaune est encore sur le carrelage.
-narrateur|La cuillère brille sur le linge.
-narrateur|Le tabouret est encore près de la table.</t>
+maman|Oui.
+maman|On ouvre ensemble.
+narrateur|Le couvercle colle un peu.
+narrateur|Puis il vient.
+narrateur|Une odeur de fleurs monte, épaisse.
+enfant-f|Ça sent l'été.
+maman|C'est du miel.
+maman|Tu goûtes avec moi ?
+enfant-f|Oui.
+narrateur|Deux cuillères trempent, toutes lentes.
+narrateur|Le fil d'or tombe, tout long.
+enfant-f|C'est collant.
+enfant-f|Et doux.
+maman|Merci, Mila.
+maman|Tu as attendu ma main.
+narrateur|Maman pose la crêpe dans l'assiette.
+narrateur|Le miel glisse au milieu, tout lent.
+enfant-f|Pour moi ?
+maman|Pour toi.
+narrateur|Mila plie la crêpe.
+narrateur|Le miel coule un peu sur le pouce.
+enfant-f|C'est bon.
+maman|La cour est calme, en bas ?
+enfant-f|Le seau brille encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1399,12 +1403,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Mila voit un pot inconnu. Que fait-elle ?</t>
+          <t>Mila voit un pot fermé. Que dit-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Mila voit un pot inconnu. Que fait-elle ?</t>
+          <t>Mila voit un pot fermé. Que dit-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1419,7 +1423,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander | à maman | un adulte | elle demande | à l'adulte</t>
+          <t>demander | je peux | à maman | un adulte | elle demande | à l'adulte</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1434,7 +1438,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle va demander. Elle parle à maman. Que fait Delphine ?</t>
+          <t>Mila parle à maman. Que dit-elle ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1483,7 +1487,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1563,8 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Mila voit un pot inconnu.
-narrateur|Que fait-elle ?</t>
+          <t>narrateur|Mila voit un pot fermé.
+narrateur|Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a demandé. L'adulte a répondu. Le pot inconnu, on en parle à maman. Tu as demandé à maman ? Oui. Bravo. On demande à un adulte. Ça sent encore le lait froid. Le rayon jaune n'a pas bougé. Le tabouret est calme. Tes mains étaient sur tes genoux ? Oui, maman.</t>
+          <t>Un fil de miel reste sur l'assiette. Mila le prend du doigt. Tu veux encore un peu ? Je peux ? Oui. Elles trempent encore la cuillère. Le pot est tiède, un peu lourd. Il n'avait pas de nom. On ne savait pas. Alors on a ouvert ensemble. La poêle ne chante plus. Il reste une odeur de beurre. Ma crêpe est douce. Tu la sens aux doigts ? Ils collent. La lumière de la cour a bougé un peu. Le seau, en bas, n'est plus au même endroit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Mila a demandé. L'adulte a répondu. Le pot inconnu, on en parle à maman. Tu as demandé à maman ? Oui. Bravo. On demande à un adulte. Ça sent encore le lait froid. Le rayon jaune n'a pas bougé. Le tabouret est calme. Tes mains étaient sur tes genoux ? Oui, maman.</t>
+          <t>Un fil de miel reste sur l'assiette. Mila le prend du doigt. Tu veux encore un peu ? Je peux ? Oui. Elles trempent encore la cuillère. Le pot est tiède, un peu lourd. Il n'avait pas de nom. On ne savait pas. Alors on a ouvert ensemble. La poêle ne chante plus. Il reste une odeur de beurre. Ma crêpe est douce. Tu la sens aux doigts ? Ils collent. La lumière de la cour a bougé un peu. Le seau, en bas, n'est plus au même endroit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1652,7 +1656,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
@@ -1739,18 +1743,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Mila a demandé.
-narrateur|L'adulte a répondu.
-narrateur|Le pot inconnu, on en parle à maman.
-maman|Tu as demandé à maman ?
-enfant-f|Oui.
-maman|Bravo.
-maman|On demande à un adulte.
-narrateur|Ça sent encore le lait froid.
-narrateur|Le rayon jaune n'a pas bougé.
-narrateur|Le tabouret est calme.
-maman|Tes mains étaient sur tes genoux ?
-enfant-f|Oui, maman.</t>
+          <t>narrateur|Un fil de miel reste sur l'assiette.
+narrateur|Mila le prend du doigt.
+maman|Tu veux encore un peu ?
+enfant-f|Je peux ?
+maman|Oui.
+narrateur|Elles trempent encore la cuillère.
+narrateur|Le pot est tiède, un peu lourd.
+enfant-f|Il n'avait pas de nom.
+maman|On ne savait pas.
+maman|Alors on a ouvert ensemble.
+narrateur|La poêle ne chante plus.
+narrateur|Il reste une odeur de beurre.
+enfant-f|Ma crêpe est douce.
+maman|Tu la sens aux doigts ?
+enfant-f|Ils collent.
+narrateur|La lumière de la cour a bougé un peu.
+narrateur|Le seau, en bas, n'est plus au même endroit.</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1786,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mila boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Maman range le pot. Le buffet est refermé. Le linge blanc est encore sur la table.</t>
+          <t>Mila boit une gorgée de lait. Le lait lave le miel de la langue. On referme le pot ? Oui, maman. Le couvercle reprend sa place, collant. C'était du miel. Oui. On le sait, maintenant. L'assiette a un rond doré, vide. Tu as encore faim ? Non. C'était bon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Mila boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, maman. Maman range le pot. Le buffet est refermé. Le linge blanc est encore sur la table.</t>
+          <t>Mila boit une gorgée de lait. Le lait lave le miel de la langue. On referme le pot ? Oui, maman. Le couvercle reprend sa place, collant. C'était du miel. Oui. On le sait, maintenant. L'assiette a un rond doré, vide. Tu as encore faim ? Non. C'était bon.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1838,7 +1847,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
@@ -1917,13 +1926,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Mila boit une gorgée d'eau.
-narrateur|L'eau est fraîche.
-maman|Le pot est rangé ?
+          <t>narrateur|Mila boit une gorgée de lait.
+narrateur|Le lait lave le miel de la langue.
+maman|On referme le pot ?
 enfant-f|Oui, maman.
-narrateur|Maman range le pot.
-narrateur|Le buffet est refermé.
-narrateur|Le linge blanc est encore sur la table.</t>
+narrateur|Le couvercle reprend sa place, collant.
+enfant-f|C'était du miel.
+maman|Oui.
+maman|On le sait, maintenant.
+narrateur|L'assiette a un rond doré, vide.
+maman|Tu as encore faim ?
+enfant-f|Non.
+enfant-f|C'était bon.</t>
         </is>
       </c>
     </row>
@@ -1950,12 +1964,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mila a vu un pot inconnu. Elle a demandé à maman. C'était du yaourt. Bravo, Mila. C'était frais.</t>
+          <t>La crêpe a laissé un rond de miel. J'ai dit je peux. Oui. La cour est pâle, en bas. Le pot doré reste entre leurs mains.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mila a vu un pot inconnu. Elle a demandé à maman. C'était du yaourt. Bravo, Mila. C'était frais.</t>
+          <t>La crêpe a laissé un rond de miel. J'ai dit je peux. Oui. La cour est pâle, en bas. Le pot doré reste entre leurs mains.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2011,14 +2025,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2090,11 +2104,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Mila a vu un pot inconnu.
-narrateur|Elle a demandé à maman.
-narrateur|C'était du yaourt.
-maman|Bravo, Mila.
-enfant-f|C'était frais.</t>
+          <t>narrateur|La crêpe a laissé un rond de miel.
+enfant-f|J'ai dit je peux.
+maman|Oui.
+narrateur|La cour est pâle, en bas.
+narrateur|Le pot doré reste entre leurs mains.</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2179,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
